--- a/data/raw/inventory/Week 33/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F11" t="n">
         <v>296</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
         <v>7</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F18" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="L18" t="n">
         <v>6</v>
@@ -1639,7 +1639,7 @@
         <v>134</v>
       </c>
       <c r="F20" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>135</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
         <v>12</v>
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F32" t="n">
         <v>54</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F35" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F42" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F45" t="n">
         <v>356</v>
@@ -3201,10 +3201,10 @@
         <v>12</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L45" t="n">
         <v>5</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F68" t="n">
         <v>34</v>
@@ -4627,10 +4627,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K68" t="n">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L68" t="n">
         <v>27</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>9</v>
       </c>
       <c r="K77" t="n">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="L77" t="n">
         <v>35</v>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F105" t="n">
         <v>171</v>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L105" t="n">
         <v>1</v>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F128" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8521,7 +8521,7 @@
         <v>150</v>
       </c>
       <c r="F131" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K131" t="n">
         <v>150</v>
@@ -10381,7 +10381,7 @@
         <v>125</v>
       </c>
       <c r="F161" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -10393,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K161" t="n">
         <v>125</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F164" t="n">
         <v>46</v>
@@ -10579,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
